--- a/elite-data/manifest-templates/EL_template_BiospecimenNonHumanTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_BiospecimenNonHumanTemplate.xlsx
@@ -171,7 +171,7 @@
     <t>BiospecimenNonHumanTemplate</t>
   </si>
   <si>
-    <t>fasle</t>
+    <t>false</t>
   </si>
   <si>
     <t>blood</t>
@@ -28513,7 +28513,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="7" t="s">

--- a/elite-data/manifest-templates/EL_template_BiospecimenNonHumanTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_BiospecimenNonHumanTemplate.xlsx
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="315">
   <si>
     <t>Filename</t>
   </si>
@@ -183,6 +183,9 @@
     <t>amygdala</t>
   </si>
   <si>
+    <t>captive</t>
+  </si>
+  <si>
     <t>bulk cell</t>
   </si>
   <si>
@@ -207,13 +210,16 @@
     <t>amygdaloid complex</t>
   </si>
   <si>
+    <t>Human</t>
+  </si>
+  <si>
     <t>bulk nuclei</t>
   </si>
   <si>
     <t>arachnoid</t>
   </si>
   <si>
-    <t>Not applicable</t>
+    <t>not applicable</t>
   </si>
   <si>
     <t>TRUE</t>
@@ -237,7 +243,7 @@
     <t>astrocytes</t>
   </si>
   <si>
-    <t>Not collected</t>
+    <t>not collected</t>
   </si>
   <si>
     <t>anxiety-related behavior</t>
@@ -261,6 +267,9 @@
     <t>Bursa Of Fabricius</t>
   </si>
   <si>
+    <t>other</t>
+  </si>
+  <si>
     <t>CD138+</t>
   </si>
   <si>
@@ -273,10 +282,13 @@
     <t>cerebrospinal fluid</t>
   </si>
   <si>
+    <t>Unknown</t>
+  </si>
+  <si>
     <t>CD8+ T-Cells</t>
   </si>
   <si>
-    <t>Unknown</t>
+    <t>unknown</t>
   </si>
   <si>
     <t>plasma</t>
@@ -291,6 +303,9 @@
     <t>Buccal Mucosa</t>
   </si>
   <si>
+    <t>wild</t>
+  </si>
+  <si>
     <t>single cell</t>
   </si>
   <si>
@@ -484,9 +499,6 @@
   </si>
   <si>
     <t>electrochemiluminescence</t>
-  </si>
-  <si>
-    <t>other</t>
   </si>
   <si>
     <t>fecal material</t>
@@ -28416,6 +28428,9 @@
     </row>
   </sheetData>
   <dataValidations>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="M2:M1000">
+      <formula1>Sheet2!$M$2:$M$8</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="D2:D1000">
       <formula1>Sheet2!$D$2:$D$4</formula1>
     </dataValidation>
@@ -28528,258 +28543,279 @@
       <c r="J2" s="7" t="s">
         <v>22</v>
       </c>
+      <c r="M2" s="7" t="s">
+        <v>23</v>
+      </c>
       <c r="N2" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="D3" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="D4" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>33</v>
-      </c>
       <c r="F4" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
       <c r="E5" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="M5" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="7" t="s">
-        <v>44</v>
-      </c>
       <c r="N5" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="E6" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>20</v>
       </c>
+      <c r="M6" s="7" t="s">
+        <v>51</v>
+      </c>
       <c r="N6" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="E7" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8">
       <c r="E8" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>58</v>
+        <v>62</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9">
       <c r="E9" s="7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
       <c r="E10" s="7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11">
       <c r="E11" s="7" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12">
       <c r="E12" s="7" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13">
       <c r="E13" s="7" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -28787,957 +28823,957 @@
         <v>9</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
       <c r="E15" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16">
       <c r="E16" s="7" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17">
       <c r="F17" s="7" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18">
       <c r="F18" s="7" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19">
       <c r="F19" s="7" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20">
       <c r="F20" s="7" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="O20" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21">
       <c r="F21" s="7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22">
       <c r="F22" s="7" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23">
       <c r="F23" s="7" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O23" s="7" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24">
       <c r="F24" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="O24" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25">
       <c r="F25" s="7" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26">
       <c r="F26" s="7" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="O26" s="7" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27">
       <c r="F27" s="7" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="O27" s="7" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28">
       <c r="F28" s="7" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="O28" s="7" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29">
       <c r="F29" s="7" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="O29" s="7" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30">
       <c r="F30" s="7" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="O30" s="7" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31">
       <c r="F31" s="7" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="O31" s="7" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32">
       <c r="F32" s="7" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="O32" s="7" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33">
       <c r="F33" s="7" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34">
       <c r="F34" s="7" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="O34" s="7" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35">
       <c r="F35" s="7" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O35" s="7" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="36">
       <c r="F36" s="7" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="O36" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37">
       <c r="F37" s="7" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="O37" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38">
       <c r="F38" s="7" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="O38" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39">
       <c r="F39" s="7" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="O39" s="7" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="40">
       <c r="F40" s="7" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="O40" s="7" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41">
       <c r="F41" s="7" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="O41" s="7" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="42">
       <c r="F42" s="7" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="O42" s="7" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="43">
       <c r="F43" s="7" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O43" s="7" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="44">
       <c r="F44" s="7" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="O44" s="7" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45">
       <c r="F45" s="7" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="O45" s="7" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="46">
       <c r="F46" s="7" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="O46" s="7" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="47">
       <c r="F47" s="7" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="O47" s="7" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48">
       <c r="F48" s="7" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="O48" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49">
       <c r="F49" s="7" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="50">
       <c r="F50" s="7" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="51">
       <c r="F51" s="7" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="52">
       <c r="F52" s="7" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="53">
       <c r="F53" s="7" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="54">
       <c r="F54" s="7" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="55">
       <c r="F55" s="7" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="56">
       <c r="F56" s="7" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="57">
       <c r="F57" s="7" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58">
       <c r="F58" s="7" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="59">
       <c r="F59" s="7" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="60">
       <c r="F60" s="7" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="61">
       <c r="F61" s="7" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="62">
       <c r="F62" s="7" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="63">
       <c r="F63" s="7" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="64">
       <c r="F64" s="7" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="65">
       <c r="F65" s="7" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66">
       <c r="F66" s="7" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="67">
       <c r="F67" s="7" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="68">
       <c r="F68" s="7" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="69">
       <c r="F69" s="7" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="70">
       <c r="F70" s="7" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="71">
       <c r="F71" s="7" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="72">
       <c r="F72" s="7" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="73">
       <c r="F73" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="74">
       <c r="F74" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="75">
       <c r="F75" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="76">
       <c r="F76" s="7" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="77">
       <c r="F77" s="7" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="78">
       <c r="F78" s="7" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="79">
       <c r="F79" s="7" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="80">
       <c r="F80" s="7" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="81">
       <c r="F81" s="7" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="82">
       <c r="F82" s="7" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="83">
       <c r="F83" s="7" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="84">
       <c r="F84" s="7" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="85">
       <c r="F85" s="7" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="86">
       <c r="F86" s="7" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="87">
       <c r="F87" s="7" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="88">
       <c r="F88" s="7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="89">
       <c r="F89" s="7" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="90">
       <c r="F90" s="7" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="91">
       <c r="F91" s="7" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="92">
       <c r="F92" s="7" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="93">
       <c r="F93" s="7" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="94">
       <c r="F94" s="7" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="95">
       <c r="F95" s="7" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="96">
       <c r="F96" s="7" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="97">
       <c r="F97" s="7" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="98">
       <c r="F98" s="7" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="99">
       <c r="F99" s="7" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="100">
       <c r="F100" s="7" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="101">
       <c r="F101" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="102">
       <c r="F102" s="7" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="103">
       <c r="F103" s="7" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="104">
       <c r="F104" s="7" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="105">
       <c r="F105" s="7" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="106">
       <c r="F106" s="7" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="107">
       <c r="F107" s="7" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="108">
       <c r="F108" s="7" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="109">
       <c r="F109" s="7" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="110">
       <c r="F110" s="7" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="111">
       <c r="F111" s="7" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="112">
       <c r="F112" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="113">
       <c r="F113" s="7" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="114">
       <c r="F114" s="7" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="115">
       <c r="F115" s="7" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="116">
       <c r="F116" s="7" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="117">
       <c r="F117" s="7" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="118">
       <c r="F118" s="7" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="119">
       <c r="F119" s="7" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="120">
       <c r="F120" s="7" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="121">
       <c r="F121" s="7" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="122">
       <c r="F122" s="7" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="123">
       <c r="F123" s="7" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
